--- a/health_tracking_forms/027_health_services_availability_form--health_tracking_forms.xlsx
+++ b/health_tracking_forms/027_health_services_availability_form--health_tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Output File</t>
+          <t>Output File Name</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>Form Ids</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category Name</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Description Name</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Output File</t>
+          <t>Output File Version</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Assigned Tool Version</t>
+          <t>Assigned Tool Version Name</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>form_version</t>
+          <t>form_version_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Form Version</t>
+          <t>Form Version 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Form Version</t>
+          <t>Form Version Name</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Version</t>
+          <t>Version Name</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'service_1'}</t>
+          <t>service_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'service_1'}</t>
+          <t>service 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'service_2'}</t>
+          <t>service_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'service_2'}</t>
+          <t>service 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'service_3'}</t>
+          <t>service_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'service_3'}</t>
+          <t>service 3</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
